--- a/SWAD2.xlsx
+++ b/SWAD2.xlsx
@@ -19,7 +19,7 @@
     <t>10036987</t>
   </si>
   <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
+    <t>S/Q CHOCO CASHW 52 G</t>
   </si>
   <si>
     <t>SWAD2</t>

--- a/SWAD2.xlsx
+++ b/SWAD2.xlsx
@@ -34,7 +34,7 @@
     <t>20008798</t>
   </si>
   <si>
-    <t>S/Q CHUNKY CASHEW 82</t>
+    <t>S/Q CHUNKY CSHW 82 G</t>
   </si>
   <si>
     <t>2</t>
